--- a/Ft-Cloud/ft-services/ft-service-pm/src/main/resources/template/importClimateCondition.xlsx
+++ b/Ft-Cloud/ft-services/ft-service-pm/src/main/resources/template/importClimateCondition.xlsx
@@ -7,7 +7,7 @@
     <workbookView windowWidth="27260" windowHeight="11920"/>
   </bookViews>
   <sheets>
-    <sheet name="2023-07-05" sheetId="1" r:id="rId1"/>
+    <sheet name="气候条件" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="144525"/>
 </workbook>
@@ -39,10 +39,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="23">
     <font>
@@ -65,11 +65,130 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="11"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -81,67 +200,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
@@ -149,68 +208,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -231,6 +231,132 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -243,7 +369,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -255,163 +393,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -443,17 +443,38 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -473,27 +494,10 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -502,8 +506,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -523,17 +527,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
+      <left/>
+      <right/>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -542,148 +542,148 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="27" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="30" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Ft-Cloud/ft-services/ft-service-pm/src/main/resources/template/importClimateCondition.xlsx
+++ b/Ft-Cloud/ft-services/ft-service-pm/src/main/resources/template/importClimateCondition.xlsx
@@ -4,34 +4,53 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27260" windowHeight="11920"/>
+    <workbookView windowWidth="27260" windowHeight="11280"/>
   </bookViews>
   <sheets>
     <sheet name="气候条件" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="144525" concurrentCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5">
   <si>
-    <t>旱季-周期</t>
+    <t>旱季</t>
   </si>
   <si>
-    <t>旱季气温</t>
+    <t>雨季</t>
   </si>
   <si>
-    <t>旱季-月均降雨量（mm）</t>
+    <t>周期</t>
   </si>
   <si>
-    <t>雨季-周期</t>
+    <t>气温</t>
   </si>
   <si>
-    <t>雨季-气温</t>
-  </si>
-  <si>
-    <t>雨季-月均降雨量（mm）</t>
+    <r>
+      <t>月均降雨量（</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>mm</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="方正书宋_GBK"/>
+        <charset val="134"/>
+      </rPr>
+      <t>）</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -39,10 +58,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="23">
     <font>
@@ -55,25 +74,103 @@
     <font>
       <b/>
       <sz val="10"/>
-      <color indexed="9"/>
-      <name val="Arial"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="方正书宋_GBK"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -87,106 +184,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -200,20 +200,41 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="34">
@@ -243,18 +264,114 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -267,7 +384,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -279,139 +402,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -426,16 +447,16 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="23"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color indexed="23"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color indexed="23"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color indexed="23"/>
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
@@ -449,17 +470,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -494,11 +509,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -507,7 +528,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -542,159 +563,156 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="30" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="17" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1016,8 +1034,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr/>
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="1" outlineLevelCol="5"/>
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="2" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="2" width="16.7211538461538" customWidth="1"/>
     <col min="3" max="3" width="24.0384615384615" customWidth="1"/>
@@ -1029,31 +1047,40 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
+      <c r="D2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
-    <row r="2" ht="14" customHeight="1" spans="1:6">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-    </row>
+    <row r="3" ht="14" customHeight="1"/>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="D1:F1"/>
+  </mergeCells>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>

--- a/Ft-Cloud/ft-services/ft-service-pm/src/main/resources/template/importClimateCondition.xlsx
+++ b/Ft-Cloud/ft-services/ft-service-pm/src/main/resources/template/importClimateCondition.xlsx
@@ -29,6 +29,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="方正书宋_GBK"/>
+        <charset val="134"/>
+      </rPr>
       <t>月均降雨量（</t>
     </r>
     <r>
@@ -58,10 +65,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="23">
     <font>
@@ -80,14 +87,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="0"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -95,9 +102,25 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -108,56 +131,27 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -170,7 +164,29 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -186,17 +202,24 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -207,24 +230,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -258,31 +265,127 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -294,25 +397,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -324,115 +427,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -461,54 +468,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -528,7 +487,22 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -550,6 +524,39 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -563,157 +570,160 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="16" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1034,8 +1044,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr/>
-  <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="2" outlineLevelCol="5"/>
+  <dimension ref="A1:F46"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="2" width="16.7211538461538" customWidth="1"/>
     <col min="3" max="3" width="24.0384615384615" customWidth="1"/>
@@ -1075,7 +1085,358 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" ht="14" customHeight="1"/>
+    <row r="3" ht="14" customHeight="1" spans="1:6">
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+    </row>
+    <row r="4" ht="14" customHeight="1" spans="1:6">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+    </row>
+    <row r="5" ht="14" customHeight="1" spans="1:6">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+    </row>
+    <row r="6" ht="14" customHeight="1" spans="1:6">
+      <c r="A6" s="2"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+    </row>
+    <row r="7" ht="14" customHeight="1" spans="1:6">
+      <c r="A7" s="2"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+    </row>
+    <row r="8" ht="14" customHeight="1" spans="1:6">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+    </row>
+    <row r="9" ht="14" customHeight="1" spans="1:6">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+    </row>
+    <row r="10" ht="14" customHeight="1" spans="1:6">
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+    </row>
+    <row r="11" ht="14" customHeight="1" spans="1:6">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+    </row>
+    <row r="12" ht="14" customHeight="1" spans="1:6">
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+    </row>
+    <row r="13" ht="14" customHeight="1" spans="1:6">
+      <c r="A13" s="2"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+    </row>
+    <row r="14" ht="14" customHeight="1" spans="1:6">
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+    </row>
+    <row r="15" ht="14" customHeight="1" spans="1:6">
+      <c r="A15" s="2"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+    </row>
+    <row r="16" ht="14" customHeight="1" spans="1:6">
+      <c r="A16" s="2"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+    </row>
+    <row r="17" ht="14" customHeight="1" spans="1:6">
+      <c r="A17" s="2"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+    </row>
+    <row r="18" ht="14" customHeight="1" spans="1:6">
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+    </row>
+    <row r="19" ht="14" customHeight="1" spans="1:6">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+    </row>
+    <row r="20" ht="14" customHeight="1" spans="1:6">
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+    </row>
+    <row r="21" ht="14" customHeight="1" spans="1:6">
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+    </row>
+    <row r="22" ht="14" customHeight="1" spans="1:6">
+      <c r="A22" s="2"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+    </row>
+    <row r="23" ht="14" customHeight="1" spans="1:6">
+      <c r="A23" s="2"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+    </row>
+    <row r="24" ht="14" customHeight="1" spans="1:6">
+      <c r="A24" s="2"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+    </row>
+    <row r="25" ht="14" customHeight="1" spans="1:6">
+      <c r="A25" s="2"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+    </row>
+    <row r="26" ht="14" customHeight="1" spans="1:6">
+      <c r="A26" s="2"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+    </row>
+    <row r="27" ht="14" customHeight="1" spans="1:6">
+      <c r="A27" s="2"/>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
+    </row>
+    <row r="28" ht="14" customHeight="1" spans="1:6">
+      <c r="A28" s="2"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2"/>
+    </row>
+    <row r="29" ht="14" customHeight="1" spans="1:6">
+      <c r="A29" s="2"/>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="2"/>
+    </row>
+    <row r="30" ht="14" customHeight="1" spans="1:6">
+      <c r="A30" s="2"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="2"/>
+    </row>
+    <row r="31" ht="14" customHeight="1" spans="1:6">
+      <c r="A31" s="2"/>
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
+      <c r="F31" s="2"/>
+    </row>
+    <row r="32" ht="14" customHeight="1" spans="1:6">
+      <c r="A32" s="2"/>
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="2"/>
+      <c r="F32" s="2"/>
+    </row>
+    <row r="33" ht="14" customHeight="1" spans="1:6">
+      <c r="A33" s="2"/>
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="2"/>
+      <c r="F33" s="2"/>
+    </row>
+    <row r="34" ht="14" customHeight="1" spans="1:6">
+      <c r="A34" s="2"/>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
+      <c r="F34" s="2"/>
+    </row>
+    <row r="35" ht="14" customHeight="1" spans="1:6">
+      <c r="A35" s="2"/>
+      <c r="B35" s="2"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
+      <c r="E35" s="2"/>
+      <c r="F35" s="2"/>
+    </row>
+    <row r="36" ht="14" customHeight="1" spans="1:6">
+      <c r="A36" s="2"/>
+      <c r="B36" s="2"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="2"/>
+      <c r="F36" s="2"/>
+    </row>
+    <row r="37" ht="14" customHeight="1" spans="1:6">
+      <c r="A37" s="2"/>
+      <c r="B37" s="2"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="2"/>
+      <c r="E37" s="2"/>
+      <c r="F37" s="2"/>
+    </row>
+    <row r="38" ht="14" customHeight="1" spans="1:6">
+      <c r="A38" s="2"/>
+      <c r="B38" s="2"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
+      <c r="E38" s="2"/>
+      <c r="F38" s="2"/>
+    </row>
+    <row r="39" ht="14" customHeight="1" spans="1:6">
+      <c r="A39" s="2"/>
+      <c r="B39" s="2"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
+      <c r="E39" s="2"/>
+      <c r="F39" s="2"/>
+    </row>
+    <row r="40" ht="14" customHeight="1" spans="1:6">
+      <c r="A40" s="2"/>
+      <c r="B40" s="2"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="2"/>
+      <c r="F40" s="2"/>
+    </row>
+    <row r="41" ht="14" customHeight="1" spans="1:6">
+      <c r="A41" s="2"/>
+      <c r="B41" s="2"/>
+      <c r="C41" s="2"/>
+      <c r="D41" s="2"/>
+      <c r="E41" s="2"/>
+      <c r="F41" s="2"/>
+    </row>
+    <row r="42" ht="14" customHeight="1" spans="1:6">
+      <c r="A42" s="2"/>
+      <c r="B42" s="2"/>
+      <c r="C42" s="2"/>
+      <c r="D42" s="2"/>
+      <c r="E42" s="2"/>
+      <c r="F42" s="2"/>
+    </row>
+    <row r="43" ht="14" customHeight="1" spans="1:6">
+      <c r="A43" s="2"/>
+      <c r="B43" s="2"/>
+      <c r="C43" s="2"/>
+      <c r="D43" s="2"/>
+      <c r="E43" s="2"/>
+      <c r="F43" s="2"/>
+    </row>
+    <row r="44" ht="14" customHeight="1" spans="1:6">
+      <c r="A44" s="2"/>
+      <c r="B44" s="2"/>
+      <c r="C44" s="2"/>
+      <c r="D44" s="2"/>
+      <c r="E44" s="2"/>
+      <c r="F44" s="2"/>
+    </row>
+    <row r="45" ht="14" customHeight="1" spans="1:6">
+      <c r="A45" s="2"/>
+      <c r="B45" s="2"/>
+      <c r="C45" s="2"/>
+      <c r="D45" s="2"/>
+      <c r="E45" s="2"/>
+      <c r="F45" s="2"/>
+    </row>
+    <row r="46" ht="14" customHeight="1" spans="1:6">
+      <c r="A46" s="2"/>
+      <c r="B46" s="2"/>
+      <c r="C46" s="2"/>
+      <c r="D46" s="2"/>
+      <c r="E46" s="2"/>
+      <c r="F46" s="2"/>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:C1"/>

--- a/Ft-Cloud/ft-services/ft-service-pm/src/main/resources/template/importClimateCondition.xlsx
+++ b/Ft-Cloud/ft-services/ft-service-pm/src/main/resources/template/importClimateCondition.xlsx
@@ -67,8 +67,8 @@
   <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="23">
     <font>
@@ -87,38 +87,45 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -131,6 +138,21 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
@@ -141,7 +163,29 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -155,85 +199,41 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="15"/>
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -259,187 +259,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -468,17 +468,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -507,6 +501,45 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -524,39 +557,6 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -570,148 +570,148 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1442,6 +1442,11 @@
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="D1:F1"/>
   </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="数字格式错误！" sqref="C$1:C$1048576 F$1:F$1048576">
+      <formula1>0</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>

--- a/Ft-Cloud/ft-services/ft-service-pm/src/main/resources/template/importClimateCondition.xlsx
+++ b/Ft-Cloud/ft-services/ft-service-pm/src/main/resources/template/importClimateCondition.xlsx
@@ -66,10 +66,10 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
     <numFmt numFmtId="176" formatCode="0.00_);\(0.00\)"/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="23">
     <font>
@@ -95,14 +95,46 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -115,16 +147,24 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -140,99 +180,59 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -260,19 +260,169 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -284,163 +434,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -478,17 +478,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -503,16 +497,31 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </right>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -543,26 +552,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </right>
       <top style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -571,159 +571,165 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="21" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1051,41 +1057,43 @@
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="1" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="2" width="16.7211538461538" customWidth="1"/>
-    <col min="3" max="3" width="24.0384615384615" style="1" customWidth="1"/>
-    <col min="4" max="5" width="16.7211538461538" customWidth="1"/>
-    <col min="6" max="6" width="23.3942307692308" style="1" customWidth="1"/>
+    <col min="1" max="1" width="16.7211538461538" customWidth="1"/>
+    <col min="2" max="2" width="16.7211538461538" style="1" customWidth="1"/>
+    <col min="3" max="3" width="24.0384615384615" style="2" customWidth="1"/>
+    <col min="4" max="4" width="16.7211538461538" customWidth="1"/>
+    <col min="5" max="5" width="16.7211538461538" style="1" customWidth="1"/>
+    <col min="6" max="6" width="23.3942307692308" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="2" t="s">
+      <c r="B1" s="4"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="2"/>
-      <c r="F1" s="3"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="5"/>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="5" t="s">
         <v>4</v>
       </c>
     </row>
